--- a/src/main/resources/InternalOrganization_Field_Values.xlsx
+++ b/src/main/resources/InternalOrganization_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430C0D07-CDB1-466E-A44E-539BE8F08EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8519A97A-4C18-4092-BCED-5A3443B902EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="3" activeTab="3" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -151,41 +151,35 @@
     <t>fieldName</t>
   </si>
   <si>
-    <t>fieldMailingStreet</t>
-  </si>
-  <si>
-    <t>fieldMailingCountry</t>
-  </si>
-  <si>
-    <t>fieldMailingPostalCode</t>
-  </si>
-  <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
-    <t>fieldFirstName</t>
-  </si>
-  <si>
-    <t>fieldLastName</t>
-  </si>
-  <si>
-    <t>fieldPhone</t>
-  </si>
-  <si>
-    <t>fieldEmail</t>
-  </si>
-  <si>
-    <t>fieldMailingCity</t>
-  </si>
-  <si>
-    <t>fieldCountry2__c</t>
+    <t>Country2__c</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>MailingStreet</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +213,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF171C1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -241,7 +241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -253,6 +253,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -272,9 +273,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -312,7 +313,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -418,7 +419,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -560,7 +561,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -784,8 +785,8 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>48</v>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -869,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -880,7 +881,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
@@ -891,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>9908786788</v>
@@ -902,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>24</v>
@@ -913,7 +914,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -924,7 +925,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -935,7 +936,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
@@ -946,7 +947,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>20171</v>
@@ -957,7 +958,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>

--- a/src/main/resources/InternalOrganization_Field_Values.xlsx
+++ b/src/main/resources/InternalOrganization_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8519A97A-4C18-4092-BCED-5A3443B902EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68844C4C-68E3-4001-9449-712687B14A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="7" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="1" r:id="rId1"/>
@@ -97,9 +97,6 @@
     <t>Herndon</t>
   </si>
   <si>
-    <t>VA</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
@@ -173,13 +170,16 @@
   </si>
   <si>
     <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>VA: Virginia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +219,12 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF211A1D"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -241,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -254,6 +260,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -596,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -607,7 +614,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -618,7 +625,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -756,7 +763,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +793,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -870,10 +877,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,10 +888,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,7 +899,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>9908786788</v>
@@ -903,10 +910,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -925,7 +932,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -938,8 +945,8 @@
       <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
+      <c r="C8" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>20171</v>
@@ -958,10 +965,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1005,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>9908786798</v>
@@ -1035,10 +1042,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1046,7 +1053,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1057,10 +1064,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,7 +1075,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1079,7 +1086,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1090,10 +1097,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/InternalOrganization_Field_Values.xlsx
+++ b/src/main/resources/InternalOrganization_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68844C4C-68E3-4001-9449-712687B14A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33549A0-230F-4EA8-88DA-8598660DD0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="7" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>VA: Virginia</t>
+  </si>
+  <si>
+    <t>VA</t>
   </si>
 </sst>
 </file>
@@ -763,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/InternalOrganization_Field_Values.xlsx
+++ b/src/main/resources/InternalOrganization_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REI Projects\GovGrants Automation 2026\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33549A0-230F-4EA8-88DA-8598660DD0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245697E1-95ED-4988-A3CC-ACA4EA23A2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{2ADB9D40-81FB-44F5-AC46-A89B5F4E8BDF}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="1" r:id="rId1"/>
@@ -580,14 +580,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED470BA6-8708-4CF0-B2C5-EF741B2578C9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,7 +598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -609,7 +609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -620,7 +620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -631,7 +631,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -642,7 +642,7 @@
         <v>926927646</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -662,7 +662,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88396F45-2FFF-4754-A21D-9B04C546541E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -671,14 +671,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A9DB05-0B00-4A98-9FC7-C651680BE6AA}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -689,7 +689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -708,13 +708,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FFA402-44F3-4194-95BC-AF87BBB9EC62}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,7 +725,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -736,7 +736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -747,7 +747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -758,7 +758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -769,7 +769,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -780,7 +780,7 @@
         <v>20171</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -791,7 +791,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -811,14 +811,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2F0B9B-0D1C-441E-8138-8347B90B311F}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -829,7 +829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -840,13 +840,13 @@
         <v>29467</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" s="5"/>
     </row>
   </sheetData>
@@ -858,13 +858,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED4E39D-6BA6-4D31-BCA1-B2F0B4803773}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -886,7 +886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -897,7 +897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -908,7 +908,7 @@
         <v>9908786788</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -919,7 +919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -930,7 +930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -941,7 +941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -952,7 +952,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -963,7 +963,7 @@
         <v>20171</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -986,13 +986,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EEEF9E7-7E28-440F-BBD4-8BA71C7E537F}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1022,14 +1022,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC09EB0-D87C-4E41-BE46-78AEA78D54B3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
